--- a/output/pdf_financials_xlsx/EDY.xlsx
+++ b/output/pdf_financials_xlsx/EDY.xlsx
@@ -720,19 +720,19 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.004149</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.027828</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.021366</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.020177</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.008965000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1143,19 +1143,19 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-8.010503</v>
+        <v>-8.014652</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-11.80095</v>
+        <v>-11.828778</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-10.568211</v>
+        <v>-10.589577</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-3.645448</v>
+        <v>-3.665625</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-2.813421</v>
+        <v>-2.822386</v>
       </c>
     </row>
     <row r="28">
@@ -1197,19 +1197,19 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-8.010503</v>
+        <v>-8.014652</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-11.547311</v>
+        <v>-11.575139</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-10.276997</v>
+        <v>-10.298363</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-3.645448</v>
+        <v>-3.665625</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-2.813421</v>
+        <v>-2.822386</v>
       </c>
     </row>
     <row r="30">
@@ -1224,19 +1224,19 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-655.0758237408778</v>
+        <v>-655.4151169903405</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-450.3891410268611</v>
+        <v>-451.47453909196</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-301.4602507661909</v>
+        <v>-302.0869902425059</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-96.4882589940092</v>
+        <v>-97.02230682618843</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-59.63896374735263</v>
+        <v>-59.82900402571659</v>
       </c>
     </row>
     <row r="31">
@@ -1307,22 +1307,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.192518</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.111225</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.45031</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.141669</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.340175</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.646772</v>
       </c>
     </row>
     <row r="35">
@@ -1357,22 +1357,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.192518</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.111225</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.45031</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.141669</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.340175</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.646772</v>
       </c>
     </row>
     <row r="37">
@@ -1657,22 +1657,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.492282</v>
+        <v>0.299764</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2.252064</v>
+        <v>2.140839</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>4.243696</v>
+        <v>3.793386</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>3.905101</v>
+        <v>2.763432</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>4.246263</v>
+        <v>3.906088</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>3.838439</v>
+        <v>3.191667</v>
       </c>
     </row>
     <row r="49">
@@ -3563,16 +3563,16 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.104002</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.195087</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.198115</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-0.207132</v>
       </c>
       <c r="F124" s="3" t="n">
         <v>0</v>
@@ -3588,16 +3588,16 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.104002</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.195087</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.198115</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-0.207132</v>
       </c>
       <c r="F125" s="3" t="n">
         <v>0</v>
@@ -4006,7 +4006,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -9592,7 +9592,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
           <t>-</t>
@@ -10632,7 +10636,11 @@
           <t>Lease payments (note 9)</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
           <t>-</t>
@@ -12758,7 +12766,11 @@
           <t>Lease payments (note 18)</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E197" s="5" t="n">
         <v>-0.104002</v>
       </c>
@@ -13296,7 +13308,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E209" s="5" t="n">

--- a/output/pdf_financials_xlsx/EDY.xlsx
+++ b/output/pdf_financials_xlsx/EDY.xlsx
@@ -1170,19 +1170,19 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>0.071201</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.253639</v>
+        <v>0.337295</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0.291214</v>
+        <v>0.394031</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>0.03718</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>0.030285</v>
       </c>
     </row>
     <row r="29">
@@ -1197,19 +1197,19 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-8.014652</v>
+        <v>-7.943451</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-11.575139</v>
+        <v>-11.491483</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-10.298363</v>
+        <v>-10.195546</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-3.665625</v>
+        <v>-3.628445</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-2.822386</v>
+        <v>-2.792101</v>
       </c>
     </row>
     <row r="30">
@@ -1224,19 +1224,19 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-655.4151169903405</v>
+        <v>-649.5925046367624</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-451.47453909196</v>
+        <v>-448.2116362410935</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-302.0869902425059</v>
+        <v>-299.0710081805254</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-97.02230682618843</v>
+        <v>-96.03822106515241</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-59.82900402571659</v>
+        <v>-59.18702189183455</v>
       </c>
     </row>
     <row r="31">
@@ -2955,22 +2955,22 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.065025</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.071201</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.337295</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.394031</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.03718</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.030285</v>
       </c>
     </row>
     <row r="101">
@@ -3264,10 +3264,10 @@
         <v>0</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.126888</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.005918</v>
       </c>
       <c r="G112" s="3" t="n">
         <v>0</v>
@@ -7424,7 +7424,11 @@
           <t>Depreciation of property and equipment (note 9)</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -8896,7 +8900,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -9076,7 +9080,11 @@
           <t>Loss on disposal of property and equipment (note 9)</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>-</t>
@@ -9780,7 +9788,11 @@
           <t>Depreciation of property and equipment (note 10)</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -9866,7 +9878,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -11904,7 +11916,11 @@
           <t>Depreciation of property and equipment (note 12)</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E178" s="5" t="n">
         <v>0.065025</v>
       </c>

--- a/output/pdf_financials_xlsx/EDY.xlsx
+++ b/output/pdf_financials_xlsx/EDY.xlsx
@@ -1394,10 +1394,10 @@
         <v>0</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0</v>
+        <v>1.54685</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0</v>
+        <v>1.485656</v>
       </c>
     </row>
     <row r="38">
@@ -1494,10 +1494,10 @@
         <v>0</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0</v>
+        <v>1.54685</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0</v>
+        <v>1.485656</v>
       </c>
     </row>
     <row r="42">
@@ -1669,10 +1669,10 @@
         <v>2.763432</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>3.906088</v>
+        <v>2.359238</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>3.191667</v>
+        <v>1.706011</v>
       </c>
     </row>
     <row r="49">
@@ -1975,10 +1975,10 @@
         <v>0</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>0</v>
+        <v>3.054335</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>0</v>
+        <v>3.054335</v>
       </c>
       <c r="F60" s="3" t="n">
         <v>0</v>
@@ -2000,10 +2000,10 @@
         <v>0.9580109999999999</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>6.108864</v>
+        <v>3.054529</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>5.421901</v>
+        <v>2.367566</v>
       </c>
       <c r="F61" s="3" t="n">
         <v>5.580143</v>
@@ -2069,22 +2069,22 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.684091</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>2.697667</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>3.492628</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>3.510902</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>2.578064</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.710298</v>
       </c>
     </row>
     <row r="65">
@@ -2147,19 +2147,19 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.479389</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>1.280979</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>1.079505</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>1.061086</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>1.623389</v>
       </c>
     </row>
     <row r="68">
@@ -5428,7 +5428,11 @@
           <t>Intangible assets and goodwill (notes 11, 12)</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>GoodwillAndOtherIntangibleAssets</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -5700,7 +5704,11 @@
           <t>Lease liabilities (note 9)</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -6160,7 +6168,11 @@
           <t>Intangible assets and goodwill (note 11, 12)</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>GoodwillAndOtherIntangibleAssets</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
@@ -7106,7 +7118,11 @@
           <t>Lease liabilities (note 18)</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E71" s="5" t="n">
         <v>0.717767</v>
       </c>
@@ -8416,7 +8432,11 @@
           <t>Proceeds from equity private placement (note 12)</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
@@ -9504,7 +9524,11 @@
           <t>Proceeds from equity private placement (note 13)</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
           <t>-</t>
